--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
